--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -19165,7 +19183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19263,6 +19281,69 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1983_84_0031 'VTJ Topoľčany' ROZBITÝ prev CLUB_S1982_83_0051 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0010</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1983_84_0010 'Kvalifikace o 2. ČNHL – skupina A' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0011</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1983_84_0011 'Kvalifikace o 2. ČNHL – skupina B' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0012</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1983_84_0012 'Kvalifikace o 2. ČNHL – skupina C (série' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -48022,6 +48103,149 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0031</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0031 'VTJ Topoľčany' ROZBITÝ prev CLUB_S1982_83_0051 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0010</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1983_84_0010 'Kvalifikace o 2. ČNHL – skupina A' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0011</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1983_84_0011 'Kvalifikace o 2. ČNHL – skupina B' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0012</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1983_84_0012 'Kvalifikace o 2. ČNHL – skupina C (série' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19183,7 +19183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19287,7 +19287,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1983_84_0031 'VTJ Topoľčany' ROZBITÝ prev CLUB_S1982_83_0051 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19297,14 +19297,9 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NODE_S1983_84_0010</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1983_84_0010 'Kvalifikace o 2. ČNHL – skupina A' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19314,14 +19309,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NODE_S1983_84_0011</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1983_84_0011 'Kvalifikace o 2. ČNHL – skupina B' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19331,17 +19321,540 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NODE_S1983_84_0012</t>
-        </is>
-      </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1983_84_0012 'Kvalifikace o 2. ČNHL – skupina C (série' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Staré Město' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -25368,12 +25881,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -26134,12 +26647,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -26218,12 +26731,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -26260,12 +26773,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -26344,12 +26857,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -26421,14 +26934,9 @@
           <t>L20</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0051</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Před zahájením soutěže došlo ke změně názvu z ASVŠ Dukla Trenčín "B" na VTJ Topoľčany. || Topoľčany = TJ Kablo Mier Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **Kablo Mier** = kabelarensky podnik (Mier = mier/peace v slovenštine - 'pokoj'). city Topoľčany.</t>
+          <t>Před zahájením soutěže došlo ke změně názvu z ASVŠ Dukla Trenčín "B" na VTJ Topoľčany. || Topoľčany = TJ Kablo Mier Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. **Kablo Mier** = kabelarensky podnik (Mier = mier/peace v slovenštine - 'pokoj'). city Topoľčany. || TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -26554,12 +27062,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -26843,12 +27351,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany.</t>
+          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany. || TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>TS Topolčany</t>
+          <t>TS Topoľčany</t>
         </is>
       </c>
     </row>
@@ -27399,12 +27907,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -27446,12 +27954,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -28010,12 +28518,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -28245,12 +28753,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -28292,12 +28800,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -28423,12 +28931,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou.</t>
+          <t>Oprava city: „Kralupy" → „Kralupy nad Vltavou" (plný název). Smart fix prev: chybělo → 51/52 0063 (Lokomotiva Kralupy). Identity transition Lokomotiva → Železničáři (zatočená geneze, podobné jako Nymburk). || Kralupy nad Vltavou = HK Kralupy nL Vltavou (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub - Patterns: Sokol Kralupy, Spartak Kralupy. city Kralupy nad Vltavou. || TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Kaučuk Kralupy</t>
+          <t>Kralupy nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -29385,12 +29893,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -31061,12 +31569,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31229,12 +31737,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -31976,12 +32484,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -34271,12 +34779,12 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -35082,12 +35590,12 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb.</t>
+          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb. || TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>Lokomotiva depo Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -35448,12 +35956,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Karlovy Vary (Stará Role) = TJ Karlovarský porcelán (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (mestska cast Karlovych Var). **Karlovarský porcelán** = **svetove znamy vyrobce porcelanu (Thun, Epiag, Sankyo)**! Stará Role = mestska cast Karlovych Var. city Karlovy Vary (Stará Role).</t>
+          <t>Karlovy Vary (Stará Role) = TJ Karlovarský porcelán (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (mestska cast Karlovych Var). **Karlovarský porcelán** = **svetove znamy vyrobce porcelanu (Thun, Epiag, Sankyo)**! Stará Role = mestska cast Karlovych Var. city Karlovy Vary (Stará Role). || TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>Karlovarský porcelán Stará Role</t>
+          <t>Stará Role</t>
         </is>
       </c>
     </row>
@@ -35621,12 +36129,12 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -35794,12 +36302,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -35841,12 +36349,12 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -35925,12 +36433,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice.</t>
+          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice. || TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>Třebenice</t>
+          <t>MDPM Lovosice</t>
         </is>
       </c>
     </row>
@@ -36177,12 +36685,12 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Calex Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Calex** = vyrobce kalkulator/elektroniky (drive Calex Levice, pobocka Novy Bor). **Nový Bor** = sklarsky mesto. city Nový Bor.</t>
+          <t>Nový Bor = TJ Calex Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Calex** = vyrobce kalkulator/elektroniky (drive Calex Levice, pobocka Novy Bor). **Nový Bor** = sklarsky mesto. city Nový Bor. || TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>Calex Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -36266,12 +36774,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -36560,12 +37068,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov.</t>
+          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov. || TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Důl Jana Žižky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -36644,12 +37152,12 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -36864,12 +37372,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -37215,12 +37723,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ OSP Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). **OSP** = Okresní stavební podnik. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ OSP Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). **OSP** = Okresní stavební podnik. city Nový Bydžov. || TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>OSP Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -38788,12 +39296,12 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice.</t>
+          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice. || TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>Dopravní podnik Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -39908,12 +40416,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -40494,12 +41002,12 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -40662,12 +41170,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Staré Město u Uherského Hradiště = TJ Jiskra Staré Město (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Soused mesta UH, ranny Velkomoravsky stredisko. NE Stare Mesto-Trutnov, NE Stare Mesto-Sumperk. city Staré Město u Uherského Hradiště.</t>
+          <t>Staré Město u Uherského Hradiště = TJ Jiskra Staré Město (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Soused mesta UH, ranny Velkomoravsky stredisko. NE Stare Mesto-Trutnov, NE Stare Mesto-Sumperk. city Staré Město u Uherského Hradiště. || TBD: city 'Staré Město' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Staré Město</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -41726,12 +42234,12 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>Hulín = TJ Nářadí Pilana Hulín (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kromeriz). **Pilana** = vyrobce nářadí (pily, kotouce). city Hulín.</t>
+          <t>Hulín = TJ Nářadí Pilana Hulín (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj (okres Kromeriz). **Pilana** = vyrobce nářadí (pily, kotouce). city Hulín. || TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>Nářadí Pilana Hulín</t>
+          <t>Hulín</t>
         </is>
       </c>
     </row>
@@ -43300,12 +43808,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -43654,12 +44162,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc.</t>
+          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc. || TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Sigma ZTS Olomouc</t>
+          <t>Olomouc</t>
         </is>
       </c>
     </row>
@@ -44834,12 +45342,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -44923,12 +45431,12 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -45296,12 +45804,12 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>Sabinov = TJ ND ZŤS Sabinov (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **ND** = Národní podnik, **ZŤS** = Závody ťažkého strojárstva (slovenske strojarne). Patterns: ND-ZŤS Sabinov -&gt; ND ZŤS Sabinov. city Sabinov.</t>
+          <t>Sabinov = TJ ND ZŤS Sabinov (Wiki D42 - registr ustavy 04/2026). Slovensky/Prešovský kraj. **ND** = Národní podnik, **ZŤS** = Závody ťažkého strojárstva (slovenske strojarne). Patterns: ND-ZŤS Sabinov -&gt; ND ZŤS Sabinov. city Sabinov. || TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>ND ZŤS Sabinov</t>
+          <t>Sabinov</t>
         </is>
       </c>
     </row>
@@ -45501,12 +46009,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany.</t>
+          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany. || TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>TS Topolčany</t>
+          <t>TS Topoľčany</t>
         </is>
       </c>
     </row>
@@ -45585,12 +46093,12 @@
       </c>
       <c r="I457" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -47242,11 +47750,6 @@
           <t>CLUB_S1983_84_0031</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>CLUB_S1982_83_0051</t>
-        </is>
-      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>setrval</t>
@@ -48109,11 +48612,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -48158,21 +48661,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0031</t>
+          <t>CLUB_S1983_84_0005</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0031 'VTJ Topoľčany' ROZBITÝ prev CLUB_S1982_83_0051 (neexist.), bez jednoznačného kandidáta — ponecháno</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -48180,21 +48681,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1983_84_0010</t>
+          <t>CLUB_S1983_84_0023</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1983_84_0010 'Kvalifikace o 2. ČNHL – skupina A' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -48202,21 +48701,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1983_84_0011</t>
+          <t>CLUB_S1983_84_0025</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1983_84_0011 'Kvalifikace o 2. ČNHL – skupina B' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -48224,24 +48721,902 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NODE_S1983_84_0012</t>
+          <t>CLUB_S1983_84_0026</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1983_84_0012 'Kvalifikace o 2. ČNHL – skupina C (série' (L25, parent=NODE_S1983_84_0009) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0029</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0031</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0034</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0048</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0063</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0064</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0076</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0081</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0082</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0085</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0106</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0145</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0149</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0149</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0165</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0215</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0233</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0241</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0246</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0250</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0251</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0253</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0259</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0261</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0268</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0270</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0273</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0276</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0285</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0286</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0319</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0345</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0348</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0356</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0358</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0362</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Staré Město' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0385</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0423</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0430</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0455</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0458</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0467</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0472</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1983_84_0474</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F5"/>
+  <autoFilter ref="A1:F49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -61224,6 +62599,11 @@
           <t>CLUB_S1982_83_0131</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>TR_S1983_84_00162</t>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19183,7 +19183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19287,7 +19287,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19299,7 +19299,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19311,7 +19311,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19323,7 +19323,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19335,7 +19335,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19347,7 +19347,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19359,7 +19359,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19371,7 +19371,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19383,7 +19383,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19395,7 +19395,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19407,7 +19407,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -19419,7 +19419,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -19431,7 +19431,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -19443,7 +19443,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -19455,7 +19455,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -19467,7 +19467,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -19479,7 +19479,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -19491,7 +19491,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -19503,7 +19503,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19515,7 +19515,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -19527,7 +19527,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -19539,7 +19539,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -19551,7 +19551,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -19563,7 +19563,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -19575,7 +19575,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -19587,7 +19587,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19599,7 +19599,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -19611,7 +19611,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -19623,7 +19623,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -19635,7 +19635,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -19647,7 +19647,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -19659,7 +19659,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -19671,7 +19671,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -19683,7 +19683,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -19695,166 +19695,10 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Staré Město' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -19871,7 +19715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19930,6 +19774,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19972,6 +19821,11 @@
           <t>12 týmů + kvalifikace o I.ligu (tabulka). Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20108,6 +19962,11 @@
           <t>Opava byla potrestána odebráním 6 bodů za neoprávněný start útočníka Jiřího Pleváka ve třech utkáních; hráč měl schváleno hostování v TJ Vítkovice.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -20380,6 +20239,11 @@
           <t>ASVŠ Dukla Trenčín "B" hrála domácí utkání v Topoľčanech.</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0017</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -20889,6 +20753,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0025</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -21524,6 +21393,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0040</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -21702,6 +21576,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0046</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -22043,6 +21922,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0053</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -22295,6 +22179,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0061</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -23014,6 +22903,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0070</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -23484,6 +23378,11 @@
       <c r="K84" t="inlineStr">
         <is>
           <t>Kontejner L40</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1982_83_0086</t>
         </is>
       </c>
     </row>
@@ -25881,12 +25780,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -26647,12 +26546,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -26773,12 +26672,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -27062,12 +26961,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -27351,12 +27250,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany. || TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>TS Topoľčany</t>
+          <t>Topoľčany</t>
         </is>
       </c>
     </row>
@@ -31737,12 +31636,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -36433,12 +36332,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice. || TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Třebenice = Slavoj/Sokol Třebenice (Wiki D42 - registr ustavy 04/2026). Mesto v okrese Litomerice. Hlavni klub Sokol/Slavoj. city Třebenice.</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>MDPM Lovosice</t>
+          <t>Třebenice</t>
         </is>
       </c>
     </row>
@@ -36774,12 +36673,12 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -40416,12 +40315,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -41170,12 +41069,12 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>Staré Město u Uherského Hradiště = TJ Jiskra Staré Město (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Soused mesta UH, ranny Velkomoravsky stredisko. NE Stare Mesto-Trutnov, NE Stare Mesto-Sumperk. city Staré Město u Uherského Hradiště. || TBD: city 'Staré Město' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Staré Město u Uherského Hradiště = TJ Jiskra Staré Město (Wiki D42 - registr ustavy 04/2026). Jihomoravsky/Zlinsky kraj (okres Uherske Hradiste). Soused mesta UH, ranny Velkomoravsky stredisko. NE Stare Mesto-Trutnov, NE Stare Mesto-Sumperk. city Staré Město u Uherského Hradiště.</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>Uherské Hradiště</t>
+          <t>Staré Město u Uherského Hradiště</t>
         </is>
       </c>
     </row>
@@ -43808,12 +43707,12 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -45342,12 +45241,12 @@
       </c>
       <c r="I439" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -46009,12 +45908,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany. || TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Topoľčany = TJ TS Topoľčany (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. PARSING CHYBA: 'Topolčany' bez háčku = preklep z 'Topoľčany'. **TS** = Topoľčianske strojárne (drive Kablo Topoľčany). city Topoľčany.</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>TS Topoľčany</t>
+          <t>Topoľčany</t>
         </is>
       </c>
     </row>
@@ -48612,7 +48511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -48666,12 +48565,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0005</t>
+          <t>CLUB_S1983_84_0025</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48686,12 +48585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0023</t>
+          <t>CLUB_S1983_84_0029</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48706,12 +48605,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0025</t>
+          <t>CLUB_S1983_84_0031</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
       </c>
     </row>
@@ -48726,12 +48625,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0026</t>
+          <t>CLUB_S1983_84_0063</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48746,12 +48645,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0029</t>
+          <t>CLUB_S1983_84_0064</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48766,12 +48665,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0031</t>
+          <t>CLUB_S1983_84_0076</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48786,12 +48685,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0034</t>
+          <t>CLUB_S1983_84_0081</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48806,12 +48705,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0048</t>
+          <t>CLUB_S1983_84_0082</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48826,12 +48725,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0063</t>
+          <t>CLUB_S1983_84_0085</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48846,12 +48745,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0064</t>
+          <t>CLUB_S1983_84_0106</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48866,12 +48765,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0076</t>
+          <t>CLUB_S1983_84_0145</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48886,12 +48785,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0081</t>
+          <t>CLUB_S1983_84_0149</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48906,12 +48805,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0082</t>
+          <t>CLUB_S1983_84_0165</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48926,12 +48825,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0085</t>
+          <t>CLUB_S1983_84_0215</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48946,12 +48845,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0106</t>
+          <t>CLUB_S1983_84_0233</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48966,12 +48865,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0145</t>
+          <t>CLUB_S1983_84_0241</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -48986,12 +48885,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0149</t>
+          <t>CLUB_S1983_84_0246</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49006,12 +48905,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0149</t>
+          <t>CLUB_S1983_84_0250</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49026,12 +48925,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0165</t>
+          <t>CLUB_S1983_84_0251</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49046,12 +48945,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0215</t>
+          <t>CLUB_S1983_84_0259</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49066,12 +48965,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0233</t>
+          <t>CLUB_S1983_84_0268</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49086,12 +48985,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0241</t>
+          <t>CLUB_S1983_84_0270</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49106,12 +49005,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0246</t>
+          <t>CLUB_S1983_84_0273</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -49126,12 +49025,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0250</t>
+          <t>CLUB_S1983_84_0276</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49146,12 +49045,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0251</t>
+          <t>CLUB_S1983_84_0285</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49166,12 +49065,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0253</t>
+          <t>CLUB_S1983_84_0286</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Třebenice' → 'MDPM Lovosice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -49186,12 +49085,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0259</t>
+          <t>CLUB_S1983_84_0319</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49206,12 +49105,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0261</t>
+          <t>CLUB_S1983_84_0348</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -49226,12 +49125,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0268</t>
+          <t>CLUB_S1983_84_0356</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -49246,12 +49145,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0270</t>
+          <t>CLUB_S1983_84_0358</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49266,12 +49165,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0273</t>
+          <t>CLUB_S1983_84_0385</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49286,12 +49185,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0276</t>
+          <t>CLUB_S1983_84_0430</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49306,12 +49205,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0285</t>
+          <t>CLUB_S1983_84_0458</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49326,12 +49225,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0286</t>
+          <t>CLUB_S1983_84_0467</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -49346,277 +49245,17 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1983_84_0319</t>
+          <t>CLUB_S1983_84_0474</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0345</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0348</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0356</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0358</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0362</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Staré Město' → 'Uherské Hradiště' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0385</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0423</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0430</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0455</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0458</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0467</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0472</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'TS Topolčany' → 'TS Topoľčany' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1983_84_0474</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F49"/>
+  <autoFilter ref="A1:F36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -46806,7 +46806,7 @@
         <v>158</v>
       </c>
       <c r="M8" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>23</v>
@@ -48100,7 +48100,7 @@
         <v>186</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -19715,7 +19715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:N103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19777,6 +19777,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -20412,6 +20412,16 @@
           <t>NODE_S1983_84_0014</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0018</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0019</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20421,6 +20431,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -20454,6 +20472,8 @@
           <t>NODE_S1983_84_0014</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20463,6 +20483,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -20496,6 +20524,8 @@
           <t>NODE_S1983_84_0014</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20505,6 +20535,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -20706,6 +20744,8 @@
           <t>NODE_S1983_84_0020</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20720,6 +20760,14 @@
         <is>
           <t>ASD Dukla Jihlava "B" hrála svá domácí utkání v Písku.</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -21010,6 +21058,8 @@
           <t>NODE_S1983_84_0025</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21019,6 +21069,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="30">
@@ -21052,6 +21110,8 @@
           <t>NODE_S1983_84_0025</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21061,6 +21121,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -21094,6 +21162,8 @@
           <t>NODE_S1983_84_0025</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21103,6 +21173,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -21833,6 +21911,8 @@
           <t>NODE_S1983_84_0044</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21842,6 +21922,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -22095,6 +22183,8 @@
           <t>NODE_S1983_84_0052</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22104,6 +22194,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -22137,6 +22235,8 @@
           <t>NODE_S1983_84_0052</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22146,6 +22246,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -22268,6 +22376,16 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0063</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0065</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22277,6 +22395,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -22310,6 +22436,16 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0063</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0065</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22319,6 +22455,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -22352,6 +22496,16 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0063</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0065</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22361,6 +22515,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -22394,6 +22556,8 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22403,6 +22567,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -22436,6 +22608,8 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22445,6 +22619,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="63">
@@ -22478,6 +22660,8 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22487,6 +22671,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -22735,6 +22927,8 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22744,6 +22938,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="70">
@@ -22819,6 +23021,8 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22828,6 +23032,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -23076,6 +23288,8 @@
           <t>NODE_S1983_84_0075</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23085,6 +23299,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -23296,6 +23518,8 @@
           <t>NODE_S1983_84_0075</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23305,6 +23529,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -23595,6 +23827,8 @@
           <t>NODE_S1983_84_0086</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23604,6 +23838,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -23810,6 +24052,8 @@
           <t>NODE_S1983_84_0086</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23819,6 +24063,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -24020,6 +24272,8 @@
           <t>NODE_S1983_84_0097</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24029,6 +24283,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="100">

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -20472,8 +20477,6 @@
           <t>NODE_S1983_84_0014</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20524,8 +20527,6 @@
           <t>NODE_S1983_84_0014</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20744,8 +20745,6 @@
           <t>NODE_S1983_84_0020</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21058,8 +21057,6 @@
           <t>NODE_S1983_84_0025</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21110,8 +21107,6 @@
           <t>NODE_S1983_84_0025</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21162,8 +21157,6 @@
           <t>NODE_S1983_84_0025</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21911,8 +21904,6 @@
           <t>NODE_S1983_84_0044</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22183,8 +22174,6 @@
           <t>NODE_S1983_84_0052</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22235,8 +22224,6 @@
           <t>NODE_S1983_84_0052</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22556,8 +22543,6 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22608,8 +22593,6 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22660,8 +22643,6 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -22927,8 +22908,6 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23021,8 +23000,6 @@
           <t>NODE_S1983_84_0058</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23288,8 +23265,6 @@
           <t>NODE_S1983_84_0075</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23518,8 +23493,6 @@
           <t>NODE_S1983_84_0075</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23827,8 +23800,6 @@
           <t>NODE_S1983_84_0086</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24052,8 +24023,6 @@
           <t>NODE_S1983_84_0086</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24272,8 +24241,6 @@
           <t>NODE_S1983_84_0097</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -48577,7 +48544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48769,6 +48736,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -39,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +90,11 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -99,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -111,6 +120,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -61286,7 +61297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -61343,7 +61354,7 @@
           <t>CLUB_S1983_84_0025</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61363,7 +61374,7 @@
           <t>CLUB_S1983_84_0029</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61383,7 +61394,7 @@
           <t>CLUB_S1983_84_0031</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>TBD: prev_club_id vymazáno (mířil na neexist. ID, žádný kandidát v předchozí sezóně) [fix_broken_prev_d42]</t>
         </is>
@@ -61403,7 +61414,7 @@
           <t>CLUB_S1983_84_0063</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61423,7 +61434,7 @@
           <t>CLUB_S1983_84_0064</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61443,7 +61454,7 @@
           <t>CLUB_S1983_84_0076</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61463,7 +61474,7 @@
           <t>CLUB_S1983_84_0081</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61483,7 +61494,7 @@
           <t>CLUB_S1983_84_0082</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61503,7 +61514,7 @@
           <t>CLUB_S1983_84_0085</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>TBD: city 'Kaučuk Kralupy' → 'Kralupy nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -61523,7 +61534,7 @@
           <t>CLUB_S1983_84_0106</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61543,7 +61554,7 @@
           <t>CLUB_S1983_84_0145</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61563,7 +61574,7 @@
           <t>CLUB_S1983_84_0149</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61583,7 +61594,7 @@
           <t>CLUB_S1983_84_0165</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61603,7 +61614,7 @@
           <t>CLUB_S1983_84_0215</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61623,7 +61634,7 @@
           <t>CLUB_S1983_84_0233</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61643,7 +61654,7 @@
           <t>CLUB_S1983_84_0241</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>TBD: city 'Karlovarský porcelán Stará Role' → 'Stará Role' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61663,7 +61674,7 @@
           <t>CLUB_S1983_84_0246</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61683,7 +61694,7 @@
           <t>CLUB_S1983_84_0250</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
@@ -61703,7 +61714,7 @@
           <t>CLUB_S1983_84_0251</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61723,7 +61734,7 @@
           <t>CLUB_S1983_84_0259</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>TBD: city 'Calex Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61743,7 +61754,7 @@
           <t>CLUB_S1983_84_0268</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61763,7 +61774,7 @@
           <t>CLUB_S1983_84_0270</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61783,7 +61794,7 @@
           <t>CLUB_S1983_84_0273</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
@@ -61803,7 +61814,7 @@
           <t>CLUB_S1983_84_0276</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61823,7 +61834,7 @@
           <t>CLUB_S1983_84_0285</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61843,7 +61854,7 @@
           <t>CLUB_S1983_84_0286</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
@@ -61863,7 +61874,7 @@
           <t>CLUB_S1983_84_0319</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61883,7 +61894,7 @@
           <t>CLUB_S1983_84_0348</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
@@ -61903,7 +61914,7 @@
           <t>CLUB_S1983_84_0356</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
@@ -61923,7 +61934,7 @@
           <t>CLUB_S1983_84_0358</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61943,7 +61954,7 @@
           <t>CLUB_S1983_84_0385</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TBD: city 'Nářadí Pilana Hulín' → 'Hulín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61963,7 +61974,7 @@
           <t>CLUB_S1983_84_0430</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -61983,7 +61994,7 @@
           <t>CLUB_S1983_84_0458</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62003,7 +62014,7 @@
           <t>CLUB_S1983_84_0467</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>TBD: city 'ND ZŤS Sabinov' → 'Sabinov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
@@ -62023,11 +62034,63 @@
           <t>CLUB_S1983_84_0474</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>30_Jihomoravský L40 finále (Jihomoravský kraj) · NODE_S1983_84_0079</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Slovácká Slavia Uherské Hradiště loni jako Jiskra Staré Město), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>torzo</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>30_Jihočeský kvalifikace o KP (Jihočeský kraj) · NODE_S1983_84_0042</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>máme jen účastníky (Sokol Kluky – Spartak Kaplice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F36"/>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -108,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,6 +122,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -24372,7 +24375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24888,6 +24891,40 @@
         </is>
       </c>
       <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0079</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Slovácká Slavia Uherské Hradiště loni jako Jiskra Staré Město), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NODE_S1983_84_0042</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] torzo: máme jen účastníky (Sokol Kluky – Spartak Kaplice), chybí výsledek / odveta  [torzo-audit]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -62054,7 +62091,7 @@
           <t>30_Jihomoravský L40 finále (Jihomoravský kraj) · NODE_S1983_84_0079</t>
         </is>
       </c>
-      <c r="D37" s="7" t="inlineStr">
+      <c r="D37" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (Slovácká Slavia Uherské Hradiště loni jako Jiskra Staré Město), chybí výsledek / odveta  [torzo-audit]</t>
         </is>
@@ -62080,7 +62117,7 @@
           <t>30_Jihočeský kvalifikace o KP (Jihočeský kraj) · NODE_S1983_84_0042</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>máme jen účastníky (Sokol Kluky – Spartak Kaplice), chybí výsledek / odveta  [torzo-audit]</t>
         </is>

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -25489,7 +25489,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30_Praha L40</t>
+          <t>Praha, 4. úroveň</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -25531,7 +25531,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -25573,7 +25573,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>30_Praha L50</t>
+          <t>Praha, 5. úroveň</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -25615,7 +25615,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30_Praha L40 základní část</t>
+          <t>Praha, 4. úroveň, základní část</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -25675,7 +25675,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30_Praha L40 finále</t>
+          <t>Praha, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -25725,7 +25725,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>30_Praha L40 skupina o udržení</t>
+          <t>Praha, 4. úroveň, skupina o udržení</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -25998,7 +25998,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30_Středočeský L40</t>
+          <t>Středočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -26045,7 +26045,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>30_Středočeský L50</t>
+          <t>Středočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A</t>
+          <t>Středočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -26129,7 +26129,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B</t>
+          <t>Středočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -26171,7 +26171,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina C</t>
+          <t>Středočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 finálová skupina</t>
+          <t>Středočeský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -26255,7 +26255,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A o umístění</t>
+          <t>Středočeský, 4. úroveň, skupina A o umístění</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -26305,7 +26305,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B o umístění</t>
+          <t>Středočeský, 4. úroveň, skupina B o umístění</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -26355,7 +26355,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina C o umístěné</t>
+          <t>Středočeský, 4. úroveň, skupina C o umístěné</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -26405,7 +26405,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 Z KP se odhlásily týmy</t>
+          <t>Středočeský, 4. úroveň Z KP se odhlásily týmy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -26447,7 +26447,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30_Středočeský Kvalifikace o KP</t>
+          <t>Středočeský Kvalifikace o KP</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -26494,7 +26494,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina A (Kutná Hora ,Kolín)</t>
+          <t>Středočeský, 4. úroveň, skupina A (Kutná Hora ,Kolín)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina B (Beroun ,Příbram ,Praha Západ)</t>
+          <t>Středočeský, 4. úroveň, skupina B (Beroun ,Příbram ,Praha Západ)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -26578,7 +26578,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina C (Kladno ,….)</t>
+          <t>Středočeský, 4. úroveň, skupina C (Kladno ,….)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -26620,7 +26620,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>30_Středočeský L40 skupina D (Mladá Boleslav ,Praha Východ)</t>
+          <t>Středočeský, 4. úroveň, skupina D (Mladá Boleslav ,Praha Východ)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -26662,7 +26662,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>30_Jihočeský L40</t>
+          <t>Jihočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -26709,7 +26709,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>30_Jihočeský L50</t>
+          <t>Jihočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -26751,7 +26751,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>30_Jihočeský kvalifikace o KP</t>
+          <t>Jihočeský kvalifikace o KP</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -26798,7 +26798,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>30_Jihočeský Kvalifikace o KP</t>
+          <t>Jihočeský Kvalifikace o KP</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -26845,7 +26845,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>30_Západočeský L40</t>
+          <t>Západočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -26892,7 +26892,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>30_Západočeský L50</t>
+          <t>Západočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -26934,7 +26934,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina A</t>
+          <t>Západočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -26976,7 +26976,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina B</t>
+          <t>Západočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina C</t>
+          <t>Západočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -27060,7 +27060,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 skupina D</t>
+          <t>Západočeský, 4. úroveň, skupina D</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -27102,7 +27102,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>30_Západočeský L40 finále</t>
+          <t>Západočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -27152,7 +27152,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>30_Západočeský kvalifikace o I.třídu</t>
+          <t>Západočeský kvalifikace o I.třídu</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -27199,7 +27199,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>30_Severočeský L40</t>
+          <t>Severočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -27246,7 +27246,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>30_Severočeský L50</t>
+          <t>Severočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -27288,7 +27288,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 skupina A</t>
+          <t>Severočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -27330,7 +27330,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 skupina B</t>
+          <t>Severočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -27372,7 +27372,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 finále</t>
+          <t>Severočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>30_Severočeský L40 o udržení</t>
+          <t>Severočeský, 4. úroveň o udržení</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -27472,7 +27472,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>30_Východočeský L40</t>
+          <t>Východočeský, 4. úroveň</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -27519,7 +27519,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>30_Východočeský L50</t>
+          <t>Východočeský, 5. úroveň</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 základní část A</t>
+          <t>Východočeský, 4. úroveň, základní část A</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -27621,7 +27621,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 základní část B</t>
+          <t>Východočeský, 4. úroveň, základní část B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -27681,7 +27681,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 základní část C</t>
+          <t>Východočeský, 4. úroveň, základní část C</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -27741,7 +27741,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina o 7. -12. místo</t>
+          <t>Východočeský, 4. úroveň, skupina o 7. -12. místo</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -27841,7 +27841,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 o záchranu</t>
+          <t>Východočeský, 4. úroveň o záchranu</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -27891,7 +27891,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina A</t>
+          <t>Východočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina B</t>
+          <t>Východočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina C</t>
+          <t>Východočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -28017,7 +28017,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>30_Východočeský kvalifikace KS</t>
+          <t>Východočeský kvalifikace KS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina A</t>
+          <t>Východočeský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -28106,7 +28106,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -28156,7 +28156,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina B</t>
+          <t>Východočeský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -28198,7 +28198,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 finále</t>
+          <t>Východočeský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -28248,7 +28248,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>30_Východočeský L40 skupina C</t>
+          <t>Východočeský, 4. úroveň, skupina C</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -28290,7 +28290,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40</t>
+          <t>Jihomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -28337,7 +28337,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L50</t>
+          <t>Jihomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -28379,7 +28379,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -28463,7 +28463,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -28513,7 +28513,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>30_Jihomoravský TJ Kravsko se vzdalo postupu do kvalifikace o KP</t>
+          <t>Jihomoravský TJ Kravsko se vzdalo postupu do kvalifikace o KP</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -28560,7 +28560,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 Žďár nad Sázavou</t>
+          <t>Jihomoravský, 4. úroveň Žďár nad Sázavou</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -28602,7 +28602,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>30_Jihomoravský KVALIFIKACE O KP</t>
+          <t>Jihomoravský KVALIFIKACE O KP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -28649,7 +28649,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina A</t>
+          <t>Jihomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -28691,7 +28691,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 finále</t>
+          <t>Jihomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -28741,7 +28741,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>30_Jihomoravský L40 skupina B</t>
+          <t>Jihomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -28783,7 +28783,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40</t>
+          <t>Severomoravský, 4. úroveň</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -28830,7 +28830,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>30_Severomoravský L50</t>
+          <t>Severomoravský, 5. úroveň</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -28872,7 +28872,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina A</t>
+          <t>Severomoravský, 4. úroveň, skupina A</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -28914,7 +28914,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina B</t>
+          <t>Severomoravský, 4. úroveň, skupina B</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -28956,7 +28956,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finálová skupina</t>
+          <t>Severomoravský, 4. úroveň finálová skupina</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -28998,7 +28998,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina o 7.místo</t>
+          <t>Severomoravský, 4. úroveň, skupina o 7.místo</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -29048,7 +29048,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>30_Severomoravský Kvalifikace o KP</t>
+          <t>Severomoravský Kvalifikace o KP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -29095,7 +29095,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 1.fáze</t>
+          <t>Severomoravský, 4. úroveň 1.fáze</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina A (Olomouc)</t>
+          <t>Severomoravský, 4. úroveň, skupina A (Olomouc)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -29179,7 +29179,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 skupina B (Ostrava)</t>
+          <t>Severomoravský, 4. úroveň, skupina B (Ostrava)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -29221,7 +29221,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>30_Severomoravský L40 finále</t>
+          <t>Severomoravský, 4. úroveň, finále</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">

--- a/data/S1983_84_FINAL.xlsx
+++ b/data/S1983_84_FINAL.xlsx
@@ -62438,7 +62438,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -66398,7 +66398,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -66476,7 +66476,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -66554,7 +66554,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -66627,7 +66627,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>play off</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -66705,7 +66705,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -66778,7 +66778,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -66934,7 +66934,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>reorganizace</t>
+          <t>o udržení</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -67396,7 +67396,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -67474,7 +67474,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>setrval</t>
+          <t>udržel se</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
